--- a/outputs/descriptives/01_missingness_by_variable.xlsx
+++ b/outputs/descriptives/01_missingness_by_variable.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,10 +383,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C2">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -401,10 +401,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -419,10 +419,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C4">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -437,10 +437,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C6">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C7">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C8">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C9">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C10">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -559,32 +559,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>log1p_people_first_aid_per_100k_ifrc_2024</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="B12">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>44.2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>people_first_aid_per_100k_ifrc_2024</t>
+          <t>Paid.staff_tpt</t>
         </is>
       </c>
       <c r="B13">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>44.2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -595,14 +595,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>people_first_aid_ifrc_2024</t>
+          <t>Percentage_unocha</t>
         </is>
       </c>
       <c r="B14">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>43.3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -613,14 +613,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>funding_per_100k_unocha</t>
+          <t>Total_tpt</t>
         </is>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -631,14 +631,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_per_100k_ifrc_2024</t>
+          <t>Volunteers_tpt</t>
         </is>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -649,32 +649,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>log1p_funding_per_100k_unocha</t>
+          <t>World.Bank.Income.Group_tpt</t>
         </is>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>log1p_income_per_100k_ifrc_2024</t>
+          <t>adaptive_capacity_ndgain</t>
         </is>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -685,14 +685,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Percentage_unocha</t>
+          <t>affected_per_100k_15_24_mean_owid</t>
         </is>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -703,14 +703,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>funding_usd_unocha</t>
+          <t>affected_per_100k_15_24_sum_owid</t>
         </is>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -721,14 +721,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_ifrc_2024</t>
+          <t>coping_capacity_inform</t>
         </is>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>log1p_volunteers_staff_per_100k_ifrc_2024</t>
+          <t>funding_per_100k_unocha</t>
         </is>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -757,14 +757,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>staff_per_100k_ifrc_2024</t>
+          <t>funding_usd_unocha</t>
         </is>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -775,14 +775,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>volunteers_per_100k_ifrc_2024</t>
+          <t>gdpPerCapita_tpt</t>
         </is>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -793,14 +793,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>volunteers_staff_per_100k_ifrc_2024</t>
+          <t>hdi_undp</t>
         </is>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -811,32 +811,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NationalSociety_ifrc_2024</t>
+          <t>log1p_affected_per_100k_15_24_mean_owid</t>
         </is>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Staff_ifrc_2024</t>
+          <t>log1p_affected_per_100k_15_24_sum_owid</t>
         </is>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -847,14 +847,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Volunteers_ifrc_2024</t>
+          <t>log1p_funding_per_100k_unocha</t>
         </is>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -865,14 +865,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>volunteers_staff_total_ifrc_2024</t>
+          <t>log1p_gdpPerCapita_tpt</t>
         </is>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -883,14 +883,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adaptive_capacity_ndgain</t>
+          <t>natural_hazard_inform</t>
         </is>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -901,14 +901,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>readiness_ndgain</t>
+          <t>population_2024_pop_wb</t>
         </is>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -919,232 +919,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hdi_undp</t>
+          <t>readiness_ndgain</t>
         </is>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>population_2024_pop_wb</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>0.8</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>character</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Total_tpt</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>World.Bank.Income.Group_tpt</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>character</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>affected_per_100k_15_24_mean_owid</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>affected_per_100k_15_24_sum_owid</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>coping_capacity_inform</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>gdpPerCapita_tpt</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>log1p_affected_per_100k_15_24_mean_owid</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>log1p_affected_per_100k_15_24_sum_owid</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>log1p_gdpPerCapita_tpt</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>natural_hazard_inform</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
